--- a/extenbooks/XS1301.xlsx
+++ b/extenbooks/XS1301.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[internal-decision-record] (2026-05-06): The ST2 implementation (P21) uses NSW = E1 - (T1 + T2*LS) — direct social benefits minus taxes. Government consumption expenditure E2 (education, health, transportation from NIPA T3.16) is loaded by L17 but NOT included in the NSW computation. With E2 excluded, P21 produces a 1959-1997 overlap mean of 0.013, within 0.002 of Moos's published mean of 0.011. Including E2 at any positive alpha overshoots the 0.011 target substantially (at alpha=1.0 mean=0.071). The standard Shaikh-Tonak/Moos formula measures net fiscal transfer to workers: direct benefits minus taxes only.</t>
+          <t>[internal-decision-record] (2026-05-06): The predecessor-build implementation (P21) uses NSW = E1 - (T1 + T2*LS) — direct social benefits minus taxes. Government consumption expenditure E2 (education, health, transportation from NIPA T3.16) is loaded by L17 but NOT included in the NSW computation. With E2 excluded, P21 produces a 1959-1997 overlap mean of 0.013, within 0.002 of Moos's published mean of 0.011. Including E2 at any positive alpha overshoots the 0.011 target substantially (at alpha=1.0 mean=0.071). The standard Shaikh-Tonak/Moos formula measures net fiscal transfer to workers: direct benefits minus taxes only.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V11 benchmark range for ST2 XS1301: expected 1959-1997 overlap mean of [0.008, 0.018], centered on Moos published value of 0.011. ST2 P21 achieves mean=0.013 (within 0.002 of target). The post-2001 rise to ~8.6% of GDP in 2010 should be reproduced with extended NIPA data. Structural shift across 2001 regime boundary is a key qualitative target.</t>
+          <t>V11 benchmark range for predecessor-build XS1301: expected 1959-1997 overlap mean of [0.008, 0.018], centered on Moos published value of 0.011. predecessor-build P21 achieves mean=0.013 (within 0.002 of target). The post-2001 rise to ~8.6% of GDP in 2010 should be reproduced with extended NIPA data. Structural shift across 2001 regime boundary is a key qualitative target.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NSW/GDP extended to 2012 by Moos (2017), replicating Shaikh &amp; Tonak methodology with post-1999 NIPA revision. 1959-2012 coverage. E2 excluded from NSW per [internal-decision-record]; standard formula NSW = E1 - T1 - T2*LS. 1959-1997 overlap mean = 0.013 in ST2 (Moos published = 0.011). Post-2001 structural break: unprecedented NSW rise to 8.6% of GDP in 2010.</t>
+          <t>NSW/GDP extended to 2012 by Moos (2017), replicating Shaikh &amp; Tonak methodology with post-1999 NIPA revision. 1959-2012 coverage. E2 excluded from NSW per [internal-decision-record]; standard formula NSW = E1 - T1 - T2*LS. 1959-1997 overlap mean = 0.013 in predecessor-build (Moos published = 0.011). Post-2001 structural break: unprecedented NSW rise to 8.6% of GDP in 2010.</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NIPA vintage difference: Moos used ~2015 data pull; ST2 uses 2026 pull; minor differences in revised historical values expected</t>
+          <t>NIPA vintage difference: Moos used ~2015 data pull; predecessor-build uses 2026 pull; minor differences in revised historical values expected</t>
         </is>
       </c>
     </row>
